--- a/src/attributions/attributions_ig_traj_477.xlsx
+++ b/src/attributions/attributions_ig_traj_477.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.07392230524600776</v>
+        <v>-0.06266747629244171</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
@@ -1011,79 +1011,79 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04373378768922086</v>
+        <v>-0.02632841313387259</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9594195460963079</v>
+        <v>0.1537386223826805</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1039679059222638</v>
+        <v>-0.1022685087819037</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.07840673233985973</v>
+        <v>0.03464646059939579</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7144228042408196</v>
+        <v>0.104244281498515</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2424999992124784</v>
+        <v>-0.007529024654677335</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2379986219069447</v>
+        <v>0.0304295675028865</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5225172813634562</v>
+        <v>0.1069846750219068</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.008625197858288726</v>
+        <v>-0.1107354985180798</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
@@ -1092,10 +1092,10 @@
         <v>-0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1775113732156182</v>
+        <v>0.01803913219676015</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.1206086681053677</v>
+        <v>-0.001558732540137179</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
@@ -1107,37 +1107,37 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.08056225068802741</v>
+        <v>-0.0905310244719247</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.3685322295407091</v>
+        <v>-0.06579145507108693</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4401934078981721</v>
+        <v>0.09996311819630718</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
         <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.4516769617820394</v>
+        <v>-0.4567282558229913</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
@@ -1146,25 +1146,25 @@
         <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.4815510642934852</v>
+        <v>0.06651687107518925</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.103247701354409</v>
+        <v>0.2583527534277317</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1846746146246459</v>
+        <v>0.1157295202675113</v>
       </c>
       <c r="BE2" t="n">
         <v>-0</v>
@@ -1173,10 +1173,10 @@
         <v>-0</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.06147757731930616</v>
+        <v>0.02853886521103764</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.4400344863293001</v>
+        <v>0.1316785680464637</v>
       </c>
       <c r="BI2" t="n">
         <v>-0</v>
@@ -1191,25 +1191,25 @@
         <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.139009677419564e-10</v>
+        <v>-9.92656824125056e-11</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.2764640453879404</v>
+        <v>-0.01028536281583142</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.04725162022994783</v>
+        <v>-0.03827405368413801</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
         <v>-0</v>
@@ -1218,22 +1218,22 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.06641758734241167</v>
+        <v>-0.1393043949226437</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.3573119659312743</v>
+        <v>0.0483350282166681</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.063190468501737</v>
+        <v>0.2438202144576959</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1242,22 +1242,22 @@
         <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1364937564584255</v>
+        <v>0.1770670072915771</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.04042179528739745</v>
+        <v>0.04474963213029687</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.5196337947215857</v>
+        <v>-0.1279810069129821</v>
       </c>
       <c r="CJ2" t="n">
         <v>-0</v>
@@ -1272,19 +1272,19 @@
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.006184687627412015</v>
+        <v>0.02712302519069994</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.3032112099524255</v>
+        <v>-0.04558030301585189</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.06353644525805609</v>
+        <v>-0.08012714712066724</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1299,25 +1299,25 @@
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.07714140715686812</v>
+        <v>0.1792947180579019</v>
       </c>
       <c r="CX2" t="n">
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.06788022260618429</v>
+        <v>0.0185435517505168</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0.575874076982219</v>
+        <v>-0.1273904699583605</v>
       </c>
       <c r="DB2" t="n">
         <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
         <v>-0</v>
@@ -1326,61 +1326,61 @@
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.3329585848206604</v>
+        <v>-0.0162782089885046</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.1190923442939047</v>
+        <v>0.06841548645030307</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.0532654363227562</v>
+        <v>-0.1117925334430952</v>
       </c>
       <c r="DK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL2" t="n">
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.2519599363490753</v>
+        <v>0.05305935579762085</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.1845121208882778</v>
+        <v>0.07278821586912297</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.1790436331424002</v>
+        <v>-0.03741343668516019</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.1611798912595937</v>
+        <v>0.1644776973990114</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.5461591772514247</v>
+        <v>-0.05571979473932834</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.2918249984441483</v>
+        <v>0.05538739336170455</v>
       </c>
       <c r="EC2" t="n">
         <v>0</v>
@@ -1407,34 +1407,34 @@
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.135321380802949</v>
+        <v>0.06733860026087622</v>
       </c>
       <c r="EH2" t="n">
         <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.0893987764208279</v>
+        <v>0.07923682764867662</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.5673181812384636</v>
+        <v>-0.04719843097901491</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.1883510799144717</v>
+        <v>-0.03982644598564319</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
@@ -1443,37 +1443,37 @@
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.3155195781137519</v>
+        <v>0.05291254879694405</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.475293402604151</v>
+        <v>-0.1150814185153581</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.07530421118295404</v>
+        <v>0.1883190420115646</v>
       </c>
       <c r="EZ2" t="n">
         <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.1604993693711561</v>
+        <v>0.066420051437225</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0.5123000179251058</v>
+        <v>-0.1362513657446551</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.01759394609252958</v>
+        <v>0.1601095184348705</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,37 +1497,37 @@
         <v>0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.4606058815130893</v>
+        <v>-0.03502961403725074</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0.7984461975854076</v>
+        <v>-0.1334343652941299</v>
       </c>
       <c r="FM2" t="n">
         <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.2340363103142088</v>
+        <v>0.1697824247822911</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
         <v>0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.755500038558886</v>
+        <v>-0.09715207698204623</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0.4189204285165135</v>
+        <v>-0.05865505864570689</v>
       </c>
       <c r="FV2" t="n">
         <v>0</v>
@@ -1536,42 +1536,42 @@
         <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03289335815016297</v>
+        <v>0.04358863316372596</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.1134219160069058</v>
+        <v>-0.04510959784159468</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.001840367372236459</v>
+        <v>-0.01440496398154498</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1341896024461979</v>
+        <v>0.05082646623797547</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0205834507833465</v>
+        <v>0.002921342587855169</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1595,10 +1595,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003713293324383824</v>
+        <v>-0.008795433939850867</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1105146709082298</v>
+        <v>0.05651524327462235</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.001545106963146841</v>
+        <v>-0.005851287866955271</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1622,22 +1622,22 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03075490539912497</v>
+        <v>0.01053566980838726</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2082400688574327</v>
+        <v>0.01803912813629981</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.203440154616896</v>
+        <v>-0.004961345527989632</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
@@ -1649,52 +1649,52 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04847593109048591</v>
+        <v>-0.005694681818574296</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1208155230308707</v>
+        <v>-0.002106664372613288</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.01634781491751268</v>
+        <v>-1.197418676044849e-06</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.03081286619505477</v>
+        <v>-0.00704121234193932</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.07293180201713953</v>
+        <v>0.04138141100384915</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1305127874710252</v>
+        <v>0.03424044134127179</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
         <v>-0</v>
@@ -1703,10 +1703,10 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.122811636611727</v>
+        <v>-0.01370257157555845</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2699074082419793</v>
+        <v>0.1091152562794429</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
@@ -1715,7 +1715,7 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4552117344033011</v>
+        <v>-0.01722637730882312</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -1724,16 +1724,16 @@
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.01913994537364691</v>
+        <v>-0.0228828185535623</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.05882277635753788</v>
+        <v>0.01389824254013121</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.2411964561196828</v>
+        <v>-0.02003508850335222</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -1757,25 +1757,25 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.01042480390989947</v>
+        <v>-0.009597538983655446</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.11085718026628</v>
+        <v>-0.007001954942943371</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.02178688873454535</v>
+        <v>0.02930238160912917</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,25 +1784,25 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.06435439611323177</v>
+        <v>0.00518452896766005</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1693024839401365</v>
+        <v>0.07302834121288218</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2045428070457161</v>
+        <v>0.003413973168776801</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
@@ -1811,10 +1811,10 @@
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.003781058791979618</v>
+        <v>0.01401072969034883</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.08816861640839092</v>
+        <v>-0.04259181179493204</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
@@ -1823,64 +1823,64 @@
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.03008657126253918</v>
+        <v>-0.009985098131564927</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.01714221940531441</v>
+        <v>0.0002755466940273512</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01827449288270459</v>
+        <v>-0.0240605210372623</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.05612691869020065</v>
+        <v>0.003775763674408533</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.0118676567972195</v>
+        <v>0.006728156602489266</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.09397601064180669</v>
+        <v>-0.04197878501097545</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.04282619093372095</v>
+        <v>-0.01254319812318063</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -1892,25 +1892,25 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.04125413238726299</v>
+        <v>-0.005740923035487838</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.1943924323256848</v>
+        <v>-0.04586772044792543</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.06142913193475977</v>
+        <v>-0.0121072908499015</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
@@ -1919,10 +1919,10 @@
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.02248981147351067</v>
+        <v>0.004512080023247238</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.08078006253090575</v>
+        <v>-0.02718357355744237</v>
       </c>
       <c r="DP3" t="n">
         <v>-0</v>
@@ -1931,25 +1931,25 @@
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.01758078782392298</v>
+        <v>-0.003978617574098639</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.0219184622989156</v>
+        <v>0.02591978570332419</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.07400592036892213</v>
+        <v>0.03350193297930568</v>
       </c>
       <c r="DY3" t="n">
         <v>-0</v>
@@ -1958,37 +1958,37 @@
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.003937806262410005</v>
+        <v>0.001211526034459881</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0174781444856204</v>
+        <v>0.006637677815204255</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.01777854525480391</v>
+        <v>-0.02484650064337484</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.06671926977684163</v>
+        <v>-0.03041740724205697</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
@@ -2000,52 +2000,52 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.02539777443088822</v>
+        <v>0.005583981663958186</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.110942123839154</v>
+        <v>-0.0162768292142434</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.04234377374526319</v>
+        <v>-0.01798296855586391</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0206530650404669</v>
+        <v>0.01212462576433685</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.1022483548875084</v>
+        <v>-0.0473521335300209</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.07075178794207172</v>
+        <v>-0.01829384367818339</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,10 +2054,10 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.05417324137779551</v>
+        <v>-0.006814328797621327</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.04919449959561894</v>
+        <v>-0.02171003426274811</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,7 +2066,7 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.04331414608214242</v>
+        <v>0.01032023270901472</v>
       </c>
       <c r="FL3" t="n">
         <v>-0</v>
@@ -2078,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.03868734772657299</v>
+        <v>0.05190382072172033</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.1374757410131204</v>
+        <v>-0.02314753550477414</v>
       </c>
       <c r="FR3" t="n">
         <v>-0</v>
@@ -2093,63 +2093,63 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.1315850966764237</v>
+        <v>0.01445744871810711</v>
       </c>
       <c r="FU3" t="n">
         <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.04553689338860291</v>
+        <v>0.02380735938504013</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.04460916176560822</v>
+        <v>-0.03058678348898084</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2967311263669043</v>
+        <v>0.3383566120373157</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1243371282553561</v>
+        <v>-0.1927565978252447</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03232240073887045</v>
+        <v>-0.08024338638081044</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2167,16 +2167,16 @@
         <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1885622356019858</v>
+        <v>0.2631860154096193</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1181468543067163</v>
+        <v>-0.2432726187984913</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06673332037533461</v>
+        <v>-0.1120100949757577</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2188,55 +2188,55 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4" t="n">
         <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1025718577882893</v>
+        <v>0.1555204844656968</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02155242606637199</v>
+        <v>-0.01888440824880626</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05431247839439249</v>
+        <v>-0.01685818923572718</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05967316875369714</v>
+        <v>0.02211764196910072</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004011626796706912</v>
+        <v>-0.1381816393098942</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.04360214510121273</v>
+        <v>-0.03188183887320463</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2245,106 +2245,106 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.06178675556153195</v>
+        <v>0.2057311046817042</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.09297876600216885</v>
+        <v>-0.0311647928705828</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.002479280102615917</v>
+        <v>0.1861893633155555</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.6286608664508008</v>
+        <v>0.6856069250009496</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.06594357043763177</v>
+        <v>-0.3279181443245037</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.2318825684014658</v>
+        <v>-0.1699426322497594</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.01328516309425498</v>
+        <v>-0.0263826117663272</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.08569674170203997</v>
+        <v>-0.0651005056720356</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.2034273009812822</v>
+        <v>-0.06526601500205687</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.02569519048390666</v>
+        <v>-0.09294772450945794</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0959329300623176</v>
+        <v>0.02834609810116329</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0834935323571728</v>
+        <v>0.1219027705620625</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,73 +2356,73 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.3137720965612235</v>
+        <v>0.4003351484286438</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002455437324004506</v>
+        <v>-0.2121611776956616</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.06374788005266327</v>
+        <v>-0.03050303998461959</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.117404382674864</v>
+        <v>-0.2359497684877344</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.06924084290794555</v>
+        <v>0.1488554562684446</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.04172717555410815</v>
+        <v>0.02400430055215374</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.006854573416516406</v>
+        <v>-0.09416413539991507</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.02196794303108688</v>
+        <v>0.04009089249980539</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.06013335050151777</v>
+        <v>0.01181880238274575</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2434,46 +2434,46 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.119639993522402</v>
+        <v>-0.2609383925019724</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.09420604023212825</v>
+        <v>0.1529386217635073</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.02870425130793349</v>
+        <v>0.05294423710817553</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.05752740788051798</v>
+        <v>-0.3152340886158623</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1124125481117109</v>
+        <v>0.207036478952898</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.181059786173927</v>
+        <v>-0.1234840317648675</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
@@ -2482,7 +2482,7 @@
         <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.1119406668738787</v>
+        <v>-0.05356335860938857</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.0004676407877270897</v>
+        <v>0.09805198417937068</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01037001256182524</v>
+        <v>-0.09224314206949036</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2518,43 +2518,43 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.03767256330740983</v>
+        <v>0.1331559359055801</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0189812003415233</v>
+        <v>0.1186731947755001</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.01313593440599418</v>
+        <v>-0.01903225030973122</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.1284736956094849</v>
+        <v>-0.1655594548378204</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.06163869802826498</v>
+        <v>0.1142830799626731</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.08091689134156738</v>
+        <v>0.07286149186668404</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
@@ -2563,7 +2563,7 @@
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,22 +2572,22 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.09569933369240385</v>
+        <v>-0.2274663465809508</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.145626128206363</v>
+        <v>0.0909645880316175</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.1308196384887312</v>
+        <v>-0.005402699615603973</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,46 +2599,46 @@
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.1286581229566808</v>
+        <v>-0.2848241367749367</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.09412196621317842</v>
+        <v>0.1784933591690668</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.05620089963172476</v>
+        <v>0.01811758409490048</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.06854724573232457</v>
+        <v>-0.1266104912449991</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0.0292025344455764</v>
+        <v>0.002317181952692989</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.009500381132614444</v>
+        <v>0.05291347356186144</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,22 +2647,22 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.006407619293051618</v>
+        <v>-0.2158282507801444</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.1379644161530533</v>
+        <v>0.4733957656728847</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.1962118813329564</v>
+        <v>0.03351618472360196</v>
       </c>
       <c r="FU4" t="n">
         <v>-0</v>
@@ -2671,34 +2671,34 @@
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01245388885188604</v>
+        <v>-0.1958125685519979</v>
       </c>
       <c r="GA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.05671222657931495</v>
+        <v>0.06463548141189318</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2706,22 +2706,22 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.09106095151019883</v>
+        <v>0.3425319370976208</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0227027353814214</v>
+        <v>-0.0008425991023005209</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.05106417298538816</v>
+        <v>-0.2233191917653046</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05332870378535402</v>
+        <v>0.2816400467028957</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,67 +2745,67 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01312379040603689</v>
+        <v>-0.1078630470710602</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.05118693199009485</v>
+        <v>-0.2159201797668562</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02076236776541407</v>
+        <v>-0.06642364786264976</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0302397464842593</v>
+        <v>-0.1223048821918709</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.004703834094670541</v>
+        <v>-0.1786261409909698</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.02837680661056069</v>
+        <v>0.1986857331956398</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01354917344336776</v>
+        <v>-0.07203963747886</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.02058214218002725</v>
+        <v>0.08332114490882343</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2817,19 +2817,19 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01747479361045546</v>
+        <v>0.1350345580677221</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.004762314508914519</v>
+        <v>0.008985824795427417</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.05072364577481836</v>
+        <v>-0.171443189188883</v>
       </c>
       <c r="AQ5" t="n">
         <v>-0</v>
@@ -2841,37 +2841,37 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1321333946042974</v>
+        <v>0.7015389489956061</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.02163129956836847</v>
+        <v>-0.3326733027227701</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.1086804575535785</v>
+        <v>-0.397661807406017</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.04713453662707309</v>
+        <v>0.1275018174356217</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,16 +2880,16 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.04178367165887896</v>
+        <v>0.03550894088812478</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.02923181369820634</v>
+        <v>-0.1646584401278237</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>-0</v>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0374961108287754</v>
+        <v>0.09146991975425604</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
@@ -2907,25 +2907,25 @@
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01916577095642134</v>
+        <v>0.1165013166664933</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01733679197139214</v>
+        <v>0.1470939458179596</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.06205022138459554</v>
+        <v>0.288246090124324</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,10 +2934,10 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.006834663503922939</v>
+        <v>-0.1429539092175082</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.03714284852555205</v>
+        <v>-0.3511896363371899</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
@@ -2949,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.03345934956174373</v>
+        <v>-0.264035838447729</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
@@ -2961,10 +2961,10 @@
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.000961215851623883</v>
+        <v>-0.03708239178464669</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.03448266880953346</v>
+        <v>0.2202846174019739</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2973,52 +2973,52 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.00443882771995708</v>
+        <v>-0.1578120438589719</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.0002882889082583769</v>
+        <v>0.03868653519167316</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.004296664971652388</v>
+        <v>0.07273499535305489</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.02711637729586333</v>
+        <v>-0.2461433628735904</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.001994239580126211</v>
+        <v>-0.0196762539459886</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.04093208486232721</v>
+        <v>0.1956744804683868</v>
       </c>
       <c r="DB5" t="n">
         <v>-0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.0267136383630086</v>
+        <v>-0.07300819582117912</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
         <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05448710995105715</v>
+        <v>-0.1093045280866914</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.01006206314727428</v>
+        <v>0.2300407829640832</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,52 +3054,52 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.008125337283557675</v>
+        <v>-0.07892289157574868</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02466796271120309</v>
+        <v>-0.03666136025640511</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.01476938916114433</v>
+        <v>0.06885832747328703</v>
       </c>
       <c r="DT5" t="n">
         <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.03007512208224923</v>
+        <v>0.177420630293667</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01870650392892687</v>
+        <v>-0.01866153872081523</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.009204101201537111</v>
+        <v>0.07309304620350275</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.02334000178325898</v>
+        <v>-0.08812037771615225</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
@@ -3123,64 +3123,64 @@
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.006764023079150562</v>
+        <v>-0.08611586934173422</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.02503123012184248</v>
+        <v>0.2273110970007435</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.01860461878049755</v>
+        <v>-0.1573678717675006</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.001951084167150453</v>
+        <v>-0.176504378935712</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01885217433926304</v>
+        <v>0.1577529199723137</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.02839979968912138</v>
+        <v>-0.2611013593385313</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.004357974670676693</v>
+        <v>-0.08108624037513124</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03824319408732094</v>
+        <v>0.2038854205142979</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3189,40 +3189,40 @@
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02070883100806223</v>
+        <v>-0.1504839565568097</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.0287354516108822</v>
+        <v>0.07329454795884233</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.03429501337367952</v>
+        <v>0.2252545632340565</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.03087087162026447</v>
+        <v>-0.05678283372570626</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
@@ -3231,63 +3231,63 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.008071120870157322</v>
+        <v>0.09483616196701011</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.001903937089670782</v>
+        <v>0.02679633035484905</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02759750990854519</v>
+        <v>-0.07547208916322203</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.02038769157087487</v>
+        <v>0.1653036708838605</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2783340420186562</v>
+        <v>0.4073789921469968</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05965177272325718</v>
+        <v>-0.1197842811284517</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03863663468154413</v>
+        <v>-0.1079891839958397</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3299,22 +3299,22 @@
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1589011538086121</v>
+        <v>0.3132179726869023</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.04617831308874955</v>
+        <v>-0.1548486215258948</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04360788479371751</v>
+        <v>-0.1229185609891293</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3323,28 +3323,28 @@
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1027514254605619</v>
+        <v>0.1586265206861765</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.03489814568118799</v>
+        <v>0.03070089558106995</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.009048210658396576</v>
+        <v>-0.0536022570089305</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
@@ -3356,25 +3356,25 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06597582419451942</v>
+        <v>0.02509531930291559</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.01793454075474684</v>
+        <v>-0.1241699593636792</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.06168821477109569</v>
+        <v>-0.079421088851683</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3383,73 +3383,73 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.04169612686406859</v>
+        <v>0.2236975926156465</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.03812325824615498</v>
+        <v>0.02459933299468891</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.05070893172383754</v>
+        <v>0.1052245564775129</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4566492875011074</v>
+        <v>0.5751256221961132</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.06693409070500764</v>
+        <v>-0.2507817018284169</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.09827686317101138</v>
+        <v>-0.2847078080212708</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0513877355973853</v>
+        <v>0.02023865849533749</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.06247363764844457</v>
+        <v>-0.1221771582054548</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.16092679478232</v>
+        <v>-0.04740161309888469</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,22 +3467,22 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.07030395604754876</v>
+        <v>-0.05461131426323418</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.08734590133177592</v>
+        <v>0.07295816281790626</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.099629636066959</v>
+        <v>0.1455945809591113</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,19 +3494,19 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2124535163510439</v>
+        <v>0.4113345535348</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.02651348373948315</v>
+        <v>-0.1594789540345156</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.02120176129862014</v>
+        <v>-0.06677041358700676</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3521,16 +3521,16 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.09137492823025914</v>
+        <v>-0.2164353626678275</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.04032326219849536</v>
+        <v>0.180175388360672</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.02304903909414545</v>
+        <v>0.02917384845400716</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
@@ -3542,25 +3542,25 @@
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.007929214578151891</v>
+        <v>-0.08287034986202184</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.00368371684358815</v>
+        <v>-0.006692595778492122</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.03665443371961293</v>
+        <v>0.006439315860955811</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3572,19 +3572,19 @@
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.08564013433937177</v>
+        <v>-0.2341529324608626</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.06188829592575191</v>
+        <v>0.1857003713494245</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.02223326397591749</v>
+        <v>0.0397330660581369</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3596,25 +3596,25 @@
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.06653284804422885</v>
+        <v>-0.1785939363560446</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1712430335218663</v>
+        <v>0.1429839395442684</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.007976627673415974</v>
+        <v>-0.05737770536750132</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
         <v>-0</v>
@@ -3629,19 +3629,19 @@
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.06420843421588467</v>
+        <v>-0.1482781954201533</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.03410959963502893</v>
+        <v>0.1257339968393716</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.01913146953994797</v>
+        <v>-0.1198746543709257</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3656,22 +3656,22 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.02229333259005488</v>
+        <v>0.08332718627573779</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.02702010238302337</v>
+        <v>0.1283425773678397</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0237389063729542</v>
+        <v>-0.08429602188279188</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
         <v>0</v>
@@ -3683,16 +3683,16 @@
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.08854217855542303</v>
+        <v>-0.1301424310581596</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.1011335444038158</v>
+        <v>-0.2337772033245743</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.03933051850405477</v>
+        <v>0.04578821809939695</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
@@ -3701,31 +3701,31 @@
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.07826011927384698</v>
+        <v>-0.182259505441673</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.06992296363759794</v>
+        <v>0.0976978947529723</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.02672860618074145</v>
+        <v>-0.02474824973232068</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3734,109 +3734,109 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.08159002818480067</v>
+        <v>-0.2542587882770665</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.06625016818235914</v>
+        <v>0.1947918133276196</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.03221362884845001</v>
+        <v>0.02031252607647582</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.01815598953034482</v>
+        <v>-0.06258767954087505</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.02253602035707513</v>
+        <v>-0.09814858512960672</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.03315280739025792</v>
+        <v>0.08154913713342586</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.006354346053277117</v>
+        <v>-0.1219313807012086</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.02740483616220576</v>
+        <v>0.3417802425730698</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.05155256970609735</v>
+        <v>0.134386166922138</v>
       </c>
       <c r="FU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02444299077058371</v>
+        <v>-0.1788929470241004</v>
       </c>
       <c r="GA6" t="n">
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.02400934594362283</v>
+        <v>0.06143473080473404</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>-0</v>
@@ -3844,79 +3844,79 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.03442675696904004</v>
+        <v>-0.1533361698041152</v>
       </c>
       <c r="B7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1450330629104071</v>
+        <v>0.1386755605520447</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06686095193124046</v>
+        <v>-0.1228499401372698</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.003870418296260041</v>
+        <v>0.007390076374246475</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001930097615616731</v>
+        <v>-0.1205837496090261</v>
       </c>
       <c r="K7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06575090889832269</v>
+        <v>0.07022461995782274</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.004295983109116752</v>
+        <v>-0.1820595298505868</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.00472620974163388</v>
+        <v>0.01312556815627987</v>
       </c>
       <c r="Q7" t="n">
         <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.03600033804359776</v>
+        <v>0.03417012244186161</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.072211799682628</v>
+        <v>-0.001765164580560541</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07435793717626871</v>
+        <v>-0.1191953862477121</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.05920523615897128</v>
+        <v>0.02797804518727222</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,133 +3925,133 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.02834090736984982</v>
+        <v>0.1322072578649654</v>
       </c>
       <c r="AC7" t="n">
         <v>-0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01355786072414242</v>
+        <v>-0.1408871447582174</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03201780825740636</v>
+        <v>-0.2303409699794409</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.00501525940526999</v>
+        <v>0.01997002320635904</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.009340050404172063</v>
+        <v>0.03445956952351688</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.02697506501602291</v>
+        <v>-0.08350304393684176</v>
       </c>
       <c r="AN7" t="n">
         <v>-0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.003428449945629396</v>
+        <v>-0.009861989234995004</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001089587461549725</v>
+        <v>0.008011556060184912</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.01943965768305589</v>
+        <v>-0.1445755785046496</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2616713387656419</v>
+        <v>0.08504018958512233</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.3661993853988605</v>
+        <v>-0.254211630672692</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.06307748393073581</v>
+        <v>0.0229207963922446</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.09131134155452668</v>
+        <v>-0.04185437067985213</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.01476540577536956</v>
+        <v>-0.004023189923460672</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.09596734446666418</v>
+        <v>0.06443310652844986</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.005403444078237638</v>
+        <v>-0.06522655587233311</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.005974360168515489</v>
+        <v>0.1481243424234877</v>
       </c>
       <c r="BM7" t="n">
         <v>-0</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.1014971225059181</v>
+        <v>0.06888106664570513</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01446781628743578</v>
+        <v>0.05165168024262985</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.008274728209975969</v>
+        <v>0.01290554030670433</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4060,25 +4060,25 @@
         <v>-0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.01039361498114906</v>
+        <v>-0.06937854644725799</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0929583620071314</v>
+        <v>0.1321159319515145</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.2348363988811657</v>
+        <v>-0.1357877890810517</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.02384125199761636</v>
+        <v>0.05175378353097361</v>
       </c>
       <c r="CB7" t="n">
         <v>-0</v>
@@ -4087,187 +4087,187 @@
         <v>-0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.03175143857992</v>
+        <v>0.08637590485123126</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.04802512183956024</v>
+        <v>0.00260912336498522</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02087104548099546</v>
+        <v>0.09534624830109695</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.005567253424072824</v>
+        <v>0.00848512903676675</v>
       </c>
       <c r="CK7" t="n">
         <v>-0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.01383333402067448</v>
+        <v>-0.04112465190028392</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.005114356164049686</v>
+        <v>0.01600118381120634</v>
       </c>
       <c r="CP7" t="n">
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.05662678926978892</v>
+        <v>-0.02697159823287622</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0004737574814249834</v>
+        <v>-0.005420669712654784</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.01678210882442822</v>
+        <v>0.08234628146478186</v>
       </c>
       <c r="CW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.04690520588176923</v>
+        <v>-0.0456726297070482</v>
       </c>
       <c r="CY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003251222926178219</v>
+        <v>0.05277423963378201</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01078313759073835</v>
+        <v>0.01632524827554109</v>
       </c>
       <c r="DC7" t="n">
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.04082094097345946</v>
+        <v>-0.03477028134639969</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0.05394657174157254</v>
+        <v>-0.03357483773425979</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06832628596350812</v>
+        <v>0.1707617741505001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.02041650448707504</v>
+        <v>-0.03679490594656894</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.07630721506475491</v>
+        <v>-0.09628112753840667</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.02226451445933145</v>
+        <v>0.03031345302032293</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.0009322551908789607</v>
+        <v>-0.1745451594633904</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0436896935980391</v>
+        <v>-0.005883279821761071</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0.01823468739126476</v>
+        <v>-0.000664471233142822</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.01031252154841692</v>
+        <v>0.1722022308955491</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.07783486475916865</v>
+        <v>-0.250658978032678</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.01275279650471009</v>
+        <v>-0.0316024658447696</v>
       </c>
       <c r="ED7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.0009674676889977263</v>
+        <v>0.07771445620929261</v>
       </c>
       <c r="EG7" t="n">
         <v>0</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0.1023665557936963</v>
+        <v>0.006788424077469376</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.003406490459277216</v>
+        <v>0.04777502957533322</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0.01840548230635972</v>
+        <v>0.08910624679307272</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4276,246 +4276,246 @@
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.03578929749994494</v>
+        <v>0.05410701612976363</v>
       </c>
       <c r="EP7" t="n">
         <v>0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.03260894025729532</v>
+        <v>0.06663680823161236</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.05247356700331897</v>
+        <v>0.03564921874415813</v>
       </c>
       <c r="ET7" t="n">
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0515028677897279</v>
+        <v>0.04889764588109523</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0167038426162417</v>
+        <v>0.08334439073277297</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ7" t="n">
-        <v>-0.04670166807350305</v>
+        <v>-0.05480365611551227</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.01301824870798444</v>
+        <v>0.08420288684703017</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.004655733260485195</v>
+        <v>-0.0004836975672428842</v>
       </c>
       <c r="FE7" t="n">
         <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0289029266044499</v>
+        <v>0.3329852807105858</v>
       </c>
       <c r="FH7" t="n">
         <v>0</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0.02330244137229048</v>
+        <v>0.02455309342743937</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02631856943013745</v>
+        <v>0.03241403729437079</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0.05540370672847261</v>
+        <v>0.02088555433101334</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.01274008216688875</v>
+        <v>0.2833721504608765</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.06062470345511663</v>
+        <v>-0.1822226815033961</v>
       </c>
       <c r="FS7" t="n">
         <v>0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.04489544183744385</v>
+        <v>0.1407671708198144</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0.03616530628209112</v>
+        <v>-0.002265616683954428</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
         <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0.01676630310524655</v>
+        <v>0.1739303536700374</v>
       </c>
       <c r="FZ7" t="n">
         <v>-0</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.02067228541874971</v>
+        <v>-0.007153680690628701</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0.03991787243465671</v>
+        <v>0.08032867586381048</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.09800323657861516</v>
+        <v>0.5022298168981073</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01792551930271605</v>
+        <v>0.01693519717570702</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05869234904222287</v>
+        <v>-0.2908312021753069</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06872419484553204</v>
+        <v>0.4766537366971001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.009858068922803678</v>
+        <v>-0.1228783120728451</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.03831828017248125</v>
+        <v>-0.1860870423910365</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01232153663877649</v>
+        <v>0.03747512266756919</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.01944999166982857</v>
+        <v>-0.1057199492994434</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.01221519437253408</v>
+        <v>-0.1127525797154465</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02315912248376669</v>
+        <v>0.1668498844388603</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01939655152509984</v>
+        <v>-0.111807984160292</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.01383141425269175</v>
+        <v>0.01917176494329437</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0</v>
@@ -4524,22 +4524,22 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01408525533350891</v>
+        <v>0.1978672466608439</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.00680053296605471</v>
+        <v>0.04417600896065485</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.04164431260414107</v>
+        <v>-0.1766148577413655</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,55 +4548,55 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1063312468105049</v>
+        <v>0.8518804797417799</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.001783212346276088</v>
+        <v>-0.3571522449867311</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.06944675250000111</v>
+        <v>-0.2885790496292598</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.05621413725562323</v>
+        <v>0.07405150280836247</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04080552704029124</v>
+        <v>-0.000293513165734771</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.03570701267725149</v>
+        <v>-0.2541048622167118</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
@@ -4605,34 +4605,34 @@
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.03650363652255837</v>
+        <v>0.1195419194260135</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01471694875665448</v>
+        <v>0.1351617190192071</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.007576853060235734</v>
+        <v>0.09795320963397638</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.04606542504489092</v>
+        <v>0.423353829563742</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,13 +4641,13 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.002408096182483314</v>
+        <v>-0.1085094273819439</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03060354265489785</v>
+        <v>-0.2881685238655775</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>-0</v>
@@ -4656,52 +4656,52 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.0263366556978916</v>
+        <v>-0.2906431472077748</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>3.126801201972433e-05</v>
+        <v>-0.007874606304098369</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.02257451780862481</v>
+        <v>0.1995340744369542</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.005286882697001637</v>
+        <v>-0.1743563185448453</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0004394038916220187</v>
+        <v>0.06910130163186681</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.005950586948812968</v>
+        <v>0.07370885751741391</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>0</v>
@@ -4713,19 +4713,19 @@
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.02249467520702514</v>
+        <v>-0.2759321340585247</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.001172327711245086</v>
+        <v>-0.02411022358190589</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.02631388218938977</v>
+        <v>0.1778329561672364</v>
       </c>
       <c r="DB8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.006052571973745324</v>
+        <v>-0.04252260452497317</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01217292893795845</v>
+        <v>-0.06885501898591638</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0210048275708436</v>
+        <v>0.1202471081816293</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,25 +4761,25 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.007924498412826374</v>
+        <v>-0.1463541359054892</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.03400707566708294</v>
+        <v>-0.05413676603046174</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001891294800329494</v>
+        <v>0.08679333939520401</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
@@ -4794,46 +4794,46 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02647186284877903</v>
+        <v>0.08357358116225462</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.02367251371636105</v>
+        <v>-0.0009718194157911785</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.002438097196025026</v>
+        <v>-0.02292686000762109</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02009599974013158</v>
+        <v>-0.0994415574685871</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.003861830112431935</v>
+        <v>-0.1192605089222553</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01050887004354767</v>
+        <v>0.1808176538288401</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
@@ -4842,67 +4842,67 @@
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.0211828560148888</v>
+        <v>-0.1751204209209289</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.0177602484478617</v>
+        <v>-0.1361361713399525</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.02046601636838423</v>
+        <v>0.09521357291768395</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.0248868157259847</v>
+        <v>-0.3030360256609986</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.003886422098811923</v>
+        <v>-0.05563409130762272</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.02715316192669671</v>
+        <v>0.1771862396812301</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.007848567829634286</v>
+        <v>-0.2201100865441222</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
@@ -4911,13 +4911,13 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02891512337338723</v>
+        <v>0.1551516866174078</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03000113445460817</v>
+        <v>0.1609090264376374</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
@@ -4926,10 +4926,10 @@
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.01268763256744239</v>
+        <v>-0.0951937607132827</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,43 +4938,43 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.003627699898164318</v>
+        <v>0.0932449436357897</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0.0009338413455932052</v>
+        <v>-0.004026715605942955</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02277861950055813</v>
+        <v>-0.1032681621389317</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.02313343993473324</v>
+        <v>0.06279674009777628</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4985,43 +4985,43 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3490135858397838</v>
+        <v>0.3633871470170216</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1423113163306551</v>
+        <v>-0.2393492306393949</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1096064551497399</v>
+        <v>-0.01260731305558801</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2855332406381946</v>
+        <v>0.3522521894969787</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08522436270209786</v>
+        <v>-0.2070260304819723</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1026570666122574</v>
+        <v>-0.03541860970505965</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,22 +5036,22 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09972510226469707</v>
+        <v>0.05947933398507095</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.004372349168291415</v>
+        <v>-0.03467787185407424</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1137942781962483</v>
+        <v>-0.1661714352400488</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
@@ -5063,46 +5063,46 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1504191374477127</v>
+        <v>0.03643287769908099</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.0003377614625148379</v>
+        <v>-0.1338502935851934</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.03051759998383534</v>
+        <v>-0.1164071843397286</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.004581300873733861</v>
+        <v>0.206295276672956</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.07707118696814587</v>
+        <v>-0.0990287015253672</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.09435203618044809</v>
+        <v>0.04636453541638499</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5114,22 +5114,22 @@
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4696525209880061</v>
+        <v>0.4141921025108993</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.04761820256760666</v>
+        <v>-0.1685433469222448</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.03977648110993096</v>
+        <v>-0.3040740897980893</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5144,19 +5144,19 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.09708699110297177</v>
+        <v>-0.04781958896357819</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.05922075733259551</v>
+        <v>-0.02213083028265418</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1103087509340178</v>
+        <v>-0.07637381201505751</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1076998264650577</v>
+        <v>0.004141504694538745</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.07215163704012144</v>
+        <v>0.0662824526323471</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.170620405334079</v>
+        <v>0.08606006132359682</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
@@ -5201,79 +5201,79 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2465061447272393</v>
+        <v>0.2736552136639579</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.01583118058788905</v>
+        <v>-0.1342269924756392</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.08110388939636842</v>
+        <v>-0.06849656402767772</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.09889625361829689</v>
+        <v>-0.2106542427826599</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.02050771735437664</v>
+        <v>0.200985627776488</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.01910642630067786</v>
+        <v>0.02722343801834543</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.05734207009770183</v>
+        <v>-0.04793389039391784</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.06760587342998997</v>
+        <v>0.3234901319435747</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.07356932635868821</v>
+        <v>0.06914636568462607</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,25 +5282,25 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.08340609731255753</v>
+        <v>-0.1888775143381313</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.03670556039627365</v>
+        <v>0.2107169789101685</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.01462200981053983</v>
+        <v>0.03132895232258381</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,43 +5309,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.002046263445206243</v>
+        <v>-0.005831599507492714</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1361932744710726</v>
+        <v>0.06991408098943933</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.005362744610165625</v>
+        <v>-0.03936010551658865</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.09945769205186374</v>
+        <v>-0.1497351778803245</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.08518253772927638</v>
+        <v>0.1553712251364625</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.08250067726832684</v>
+        <v>-0.0059312930543809</v>
       </c>
       <c r="DS9" t="n">
         <v>-0</v>
@@ -5354,79 +5354,79 @@
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.1159427784613421</v>
+        <v>-0.09704746316457011</v>
       </c>
       <c r="DY9" t="n">
         <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.02649124981219659</v>
+        <v>-0.09692853876058928</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04026332230697271</v>
+        <v>-0.116549097142415</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.1042183597717175</v>
+        <v>-0.09021026488984886</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0883038344827566</v>
+        <v>0.1573148974935789</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.1432891790881929</v>
+        <v>0.0480186472048422</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.0884841026534689</v>
+        <v>-0.1701225929062372</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.03589727252620472</v>
+        <v>0.0983155618226048</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.07524029347793576</v>
+        <v>0.02474709560095275</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
@@ -5435,25 +5435,25 @@
         <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.08425162380474482</v>
+        <v>-0.2125007572325717</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.04604469299533918</v>
+        <v>0.2189852684988938</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.02926223050977172</v>
+        <v>0.005920477189054412</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
@@ -5462,25 +5462,25 @@
         <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.1417917432512144</v>
+        <v>-0.01209444113375572</v>
       </c>
       <c r="FI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0570504647136985</v>
+        <v>0.127799463087759</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.06115037669534119</v>
+        <v>-0.1856844010220181</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,25 +5489,25 @@
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.01986752392038792</v>
+        <v>0.005594485455071351</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.03050253480295274</v>
+        <v>-0.03177676278907564</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.06303703174992711</v>
+        <v>0.04564837221845058</v>
       </c>
       <c r="FU9" t="n">
         <v>0</v>
@@ -5516,25 +5516,25 @@
         <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.06280468282996225</v>
+        <v>-0.09525942692154114</v>
       </c>
       <c r="GA9" t="n">
         <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.03224440487084945</v>
+        <v>0.1622804676383375</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
         <v>-0</v>
@@ -5543,15 +5543,15 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1307280594243049</v>
+        <v>0.1018555433965953</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -5560,25 +5560,25 @@
         <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1091281030954026</v>
+        <v>-0.2164241816853299</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1115402130466118</v>
+        <v>0.04048204401803501</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1211841142360065</v>
+        <v>0.06694237676835764</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -5587,25 +5587,25 @@
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03794079604804767</v>
+        <v>-0.2312867503572919</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05668342005282717</v>
+        <v>-0.01349973400370597</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02931408121301764</v>
+        <v>-0.02643511360863786</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -5614,40 +5614,40 @@
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.07823112592673913</v>
+        <v>-0.0627174397730723</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05844674286740562</v>
+        <v>-0.03317886520547874</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.03061579104903625</v>
+        <v>0.01683899214420825</v>
       </c>
       <c r="AC10" t="n">
         <v>-0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.02657483745367406</v>
+        <v>0.06921057773817277</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02881599028430756</v>
+        <v>0.1724533489772213</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -5656,49 +5656,49 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.02118043154819838</v>
+        <v>0.01012163372433703</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.02648662725268143</v>
+        <v>-0.1632492120020233</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.06115112079454185</v>
+        <v>0.07147001646794385</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.1027412195614473</v>
+        <v>-0.05733795710489991</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.08080964731833065</v>
+        <v>-0.3271760627812458</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1969537065475934</v>
+        <v>-0.0231596704229488</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5713,7 +5713,7 @@
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.1297599544994613</v>
+        <v>0.1673440184901697</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -5722,16 +5722,16 @@
         <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.01195839478717312</v>
+        <v>0.2121877243855237</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.06533884186360227</v>
+        <v>0.1317815157774842</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
         <v>0</v>
@@ -5740,19 +5740,19 @@
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.05704214637644153</v>
+        <v>0.02657397556916878</v>
       </c>
       <c r="BM10" t="n">
         <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.02289395396223207</v>
+        <v>0.02053061387496014</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1204564896781425</v>
+        <v>-0.1269927460029322</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -5761,25 +5761,25 @@
         <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.04454824990328577</v>
+        <v>-0.05995354906651924</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.003711024399113985</v>
+        <v>-0.2422008748762622</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.09147788295344046</v>
+        <v>-0.02877098559165958</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -5788,67 +5788,67 @@
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0.02923100212327914</v>
+        <v>-0.04735477421133037</v>
       </c>
       <c r="CE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0.01330987086959971</v>
+        <v>0.1149694181763745</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.03273141228984491</v>
+        <v>-0.01169564958914869</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0.02580369663144007</v>
+        <v>-0.001658855722725343</v>
       </c>
       <c r="CN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.0650193654212505</v>
+        <v>0.07836869043508594</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05473004877977612</v>
+        <v>-0.03644565584534274</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0.01616926988172304</v>
+        <v>-0.03627464312097359</v>
       </c>
       <c r="CW10" t="n">
         <v>-0</v>
@@ -5857,25 +5857,25 @@
         <v>-0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.004094842377636493</v>
+        <v>0.1141034203528671</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.02366902272242092</v>
+        <v>0.005334804958317834</v>
       </c>
       <c r="DA10" t="n">
         <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0.01652681130527175</v>
+        <v>-0.00502019173014389</v>
       </c>
       <c r="DF10" t="n">
         <v>-0</v>
@@ -5884,10 +5884,10 @@
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.07776717662502855</v>
+        <v>0.08546684545831602</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.03041839721588399</v>
+        <v>-0.02364111937631341</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
@@ -5902,103 +5902,103 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0.03119640727351811</v>
+        <v>-0.05334372926670387</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.04763205614419854</v>
+        <v>0.002053291464939115</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.07583471829450097</v>
+        <v>0.03353996878675939</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.04197650014406051</v>
+        <v>0.0186833187929385</v>
       </c>
       <c r="DX10" t="n">
         <v>-0</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.02493979430378451</v>
+        <v>0.02693596678060193</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.03972275953566419</v>
+        <v>0.02087586088317478</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.01894192872423924</v>
+        <v>-0.07372286996942251</v>
       </c>
       <c r="EG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.02081842703658545</v>
+        <v>0.1008538701267095</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.004895514682067858</v>
+        <v>0.02662422219156832</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0.007068356506949598</v>
+        <v>0.029470557775822</v>
       </c>
       <c r="EP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.02777198333961136</v>
+        <v>0.1255116377557763</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01501837167920496</v>
+        <v>0.0106802030599594</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6010,19 +6010,19 @@
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0.01806430048151805</v>
+        <v>-0.04356339408225712</v>
       </c>
       <c r="EY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.005328578121067976</v>
+        <v>0.1440176629440477</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.03030122270302715</v>
+        <v>-0.003548326897875093</v>
       </c>
       <c r="FC10" t="n">
         <v>0</v>
@@ -6034,22 +6034,22 @@
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0.02357761783999818</v>
+        <v>0.02229771363141286</v>
       </c>
       <c r="FH10" t="n">
         <v>0</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.03088938493754291</v>
+        <v>0.08806450124516876</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.1240471649536402</v>
+        <v>0.1326485230592345</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6058,40 +6058,40 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.006129916132088909</v>
+        <v>-0.002161204159684064</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.008534469457363501</v>
+        <v>0.1880174695403454</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.06209831070758572</v>
+        <v>0.08636850977179458</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.01804134748393466</v>
+        <v>0.02296099634299061</v>
       </c>
       <c r="FZ10" t="n">
         <v>0</v>
@@ -6100,13 +6100,13 @@
         <v>-0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.01984927897792499</v>
+        <v>0.2044699492422362</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -7261,25 +7261,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4459139605388348</v>
+        <v>0.3592917935336568</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1711330777568468</v>
+        <v>-0.1822069604631978</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01616988667344876</v>
+        <v>-0.05254690095872761</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,22 +7288,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2618107514096871</v>
+        <v>0.3408055574390248</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1917004097745215</v>
+        <v>-0.2374002805964152</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01812509689253198</v>
+        <v>-0.1235931378621014</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -7315,79 +7315,79 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1021721138145846</v>
+        <v>0.04775032753295088</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.007561784910812288</v>
+        <v>-0.07491931937805132</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1817898178378269</v>
+        <v>-0.08458236034779693</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.09097803958141895</v>
+        <v>-0.04843367167644803</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.04182138714347174</v>
+        <v>-0.1490813171613726</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.05083121419029316</v>
+        <v>-0.05103512472080342</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.0201885367098735</v>
+        <v>0.1146604352942754</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.05552692986647373</v>
+        <v>-0.1225944985740234</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.006854049070158962</v>
+        <v>0.07040680942751218</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
@@ -7396,25 +7396,25 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4227088442206779</v>
+        <v>0.3088633664987334</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.08627302295838786</v>
+        <v>-0.07803660751716575</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1601156040271106</v>
+        <v>-0.2313681190638241</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
@@ -7423,25 +7423,25 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.07109734788584553</v>
+        <v>0.003068198302387113</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.2304961128400876</v>
+        <v>-0.03925831785004282</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1534949780257449</v>
+        <v>-0.04214324904550549</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,22 +7450,22 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.09543424042899548</v>
+        <v>0.005034447224620759</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.001354702451692892</v>
+        <v>0.04748431044702157</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1771503592703086</v>
+        <v>0.04836103974316595</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,49 +7477,49 @@
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1463933348499534</v>
+        <v>0.176600638361126</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.04887115716612626</v>
+        <v>-0.1224450050325355</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.107454934231661</v>
+        <v>-0.06110575583003718</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1079606670261413</v>
+        <v>-0.1276800426914305</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.008899721493574932</v>
+        <v>0.119804678700344</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01861204104293668</v>
+        <v>0.01163771201990684</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7528,22 +7528,22 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0002977611295213056</v>
+        <v>-0.058264303569265</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.1593579638657537</v>
+        <v>0.1845688269146415</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.05745741747513632</v>
+        <v>0.05247798065455102</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7555,19 +7555,19 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.07636382993638191</v>
+        <v>-0.1267544144530547</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.02538397169381102</v>
+        <v>0.1286679108403761</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.03064983880963142</v>
+        <v>0.0269166744992071</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,16 +7585,16 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.02594560529068748</v>
+        <v>-0.05662569120705301</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.06421295981228808</v>
+        <v>0.03700713279092085</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.04284747518063085</v>
+        <v>-0.1133662816689006</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7609,28 +7609,28 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.06692547541697656</v>
+        <v>-0.08243507067692453</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0.005352983417534441</v>
+        <v>-0.0535132282620556</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.04614059436292036</v>
+        <v>-0.02931707492201629</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,16 +7639,16 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.04652362682878267</v>
+        <v>-0.01570417342869306</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.04456403411795447</v>
+        <v>0.07655770805560431</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.06551243866706995</v>
+        <v>-0.01291335233809971</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
@@ -7657,25 +7657,25 @@
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.09255137538525585</v>
+        <v>-0.1009031716898221</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0.02155760168327763</v>
+        <v>0.08444204066976768</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.07882399159090536</v>
+        <v>0.0598638099871014</v>
       </c>
       <c r="EK13" t="n">
         <v>0</v>
@@ -7690,22 +7690,22 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.002733288302085428</v>
+        <v>-0.03481318808594506</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.02074445381887239</v>
+        <v>0.07382035884835732</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01619622798086272</v>
+        <v>-0.0004328356836344699</v>
       </c>
       <c r="ET13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7720,25 +7720,25 @@
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.0744023790039601</v>
+        <v>-0.1395969595180931</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.02667089388386729</v>
+        <v>0.1519275651274253</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.002691731087409727</v>
+        <v>0.006348257305824758</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF13" t="n">
         <v>-0</v>
@@ -7747,16 +7747,16 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.007758052490902569</v>
+        <v>0.1181271331729368</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>-0.01087444365061169</v>
+        <v>0.09476898289366903</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.009346262036840572</v>
+        <v>0.02149967609727544</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
@@ -7768,22 +7768,22 @@
         <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.04001490333948333</v>
+        <v>0.05129330730200424</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.03351822264518432</v>
+        <v>0.1481102267885421</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.04864843545630874</v>
+        <v>-0.01661578301760633</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
@@ -7792,31 +7792,31 @@
         <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.06045739542596426</v>
+        <v>-0.06899729722858557</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.130136487789523</v>
+        <v>0.0705901951194593</v>
       </c>
       <c r="GC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
         <v>0</v>
@@ -7830,34 +7830,34 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1326502320369752</v>
+        <v>0.2776651181459337</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0411107494722151</v>
+        <v>0.001820353386143584</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07847289113626275</v>
+        <v>-0.1352775114502263</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1015654339140695</v>
+        <v>0.2958127498552545</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,64 +7866,64 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02837341785109366</v>
+        <v>-0.08216455171908965</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0618406429315027</v>
+        <v>-0.1494768224313383</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.008369677593723699</v>
+        <v>0.0779616066583397</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.006915334741019052</v>
+        <v>-0.1053765641537316</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01259152563022294</v>
+        <v>-0.0130814197651923</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.008310582139874786</v>
+        <v>-0.03784860970396196</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.01827041259334358</v>
+        <v>-0.1840348829893746</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.003780947911074912</v>
+        <v>0.04625407992502249</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7938,61 +7938,61 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.006264156523235752</v>
+        <v>0.03058308027256831</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01511100724307064</v>
+        <v>-0.03503405966989583</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.0120029533801772</v>
+        <v>0.001426767499522892</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.1048445166875283</v>
+        <v>0.2590565360452012</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.01604908423272349</v>
+        <v>-0.2365252808059892</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.01994090903714588</v>
+        <v>-0.09672251284406373</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.03777025942843452</v>
+        <v>0.002507553597560865</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,40 +8001,40 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.05006682113541237</v>
+        <v>0.009893002865848736</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.06753179705676776</v>
+        <v>-0.08021889935791235</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.03930188979199443</v>
+        <v>0.02346920452199978</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.02291916642722742</v>
+        <v>0.0729201580655504</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.01885905762802362</v>
+        <v>0.00428360500577605</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.04342455380650033</v>
+        <v>0.136331077525196</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
@@ -8055,10 +8055,10 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.007334183767998527</v>
+        <v>-0.0517041901955425</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.005084319313243417</v>
+        <v>-0.09760812703293621</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,28 +8067,28 @@
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.02406348216911706</v>
+        <v>-0.08611338931486963</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.001706809490692865</v>
+        <v>0.01135225068016776</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.02338515360418984</v>
+        <v>0.05518670583349235</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
@@ -8097,10 +8097,10 @@
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.002477362173819468</v>
+        <v>-0.02687241737477271</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,64 +8109,64 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.003330062148770469</v>
+        <v>0.1036057040916307</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.01630725702028585</v>
+        <v>0.06890295516252512</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.01925308711294443</v>
+        <v>-0.08871994929373817</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.004378235229561136</v>
+        <v>0.009943425081428989</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.02246202985655802</v>
+        <v>0.07470002864007143</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.01404712147304774</v>
+        <v>-0.0214351625138722</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.02423873589575714</v>
+        <v>-0.121265793777661</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.007877343423518512</v>
+        <v>0.07153826488800302</v>
       </c>
       <c r="DK14" t="n">
         <v>-0</v>
@@ -8181,100 +8181,100 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.008609811041685891</v>
+        <v>-0.02035198159281916</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.01559596332659499</v>
+        <v>-0.08315881311736649</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.009213534373515594</v>
+        <v>0.05035212119029489</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.03894162212250449</v>
+        <v>0.01086278456736327</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
         <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01586893952704251</v>
+        <v>-0.03412481415778065</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.01125233160535938</v>
+        <v>0.0250768929415982</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.02696857497061333</v>
+        <v>-0.04483722077387268</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
         <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.004367851483752435</v>
+        <v>0.01489739370980167</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.02033121926517888</v>
+        <v>0.005640077044255046</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.01229892614009343</v>
+        <v>-0.01587151108157569</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.003493288765557266</v>
+        <v>0.005770227554795236</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.005354124266902007</v>
+        <v>0.096915871425745</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8283,13 +8283,13 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.01956780325525801</v>
+        <v>-0.09724328736069078</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
@@ -8298,25 +8298,25 @@
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.008647587706285553</v>
+        <v>-0.008253485460282355</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.02674604858089967</v>
+        <v>0.04820286562971213</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.02499122356843736</v>
+        <v>0.1593179931443366</v>
       </c>
       <c r="FI14" t="n">
         <v>0</v>
@@ -8325,16 +8325,16 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.007503550012177985</v>
+        <v>-0.05418515547557931</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.01441407953992443</v>
+        <v>0.1217100457774709</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.004435499444264017</v>
+        <v>0.0504103689487795</v>
       </c>
       <c r="FR14" t="n">
         <v>0</v>
@@ -8352,46 +8352,46 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.01928577950279144</v>
+        <v>-0.07751087200237394</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.01073083328766289</v>
+        <v>-0.0343884670012151</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.004084987082582861</v>
+        <v>-0.03768613720243984</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.006347584905273406</v>
+        <v>0.08628876767208077</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,25 +8399,25 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4901696951351475</v>
+        <v>0.218015375605173</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1788806942893356</v>
+        <v>-0.162741310304822</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0553234248679294</v>
+        <v>-0.04127426515863692</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,16 +8426,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3105160260260293</v>
+        <v>0.2280209961467905</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1754504501704457</v>
+        <v>-0.1965289346858936</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05010791533306751</v>
+        <v>-0.07706008167756384</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8447,112 +8447,112 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1121499272529316</v>
+        <v>0.0437411909618526</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.01549765956726756</v>
+        <v>-0.04445338356060472</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1053500170614261</v>
+        <v>-0.07614530438160808</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0319868713703844</v>
+        <v>-0.06046913585651301</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.006895501756551226</v>
+        <v>-0.1003232297913557</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.01076910217063053</v>
+        <v>-0.06497480054689107</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01309160016778716</v>
+        <v>0.08404430597178038</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.06543880954054306</v>
+        <v>-0.09433618711026238</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.0537946366051516</v>
+        <v>0.02334228063923841</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4451751601285324</v>
+        <v>0.20977773467335</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0284739594241274</v>
+        <v>-0.07972479403793976</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1048899657015461</v>
+        <v>-0.1618751125263973</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
@@ -8561,25 +8561,25 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05184052230183074</v>
+        <v>-0.01458335936988389</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.1888185229410483</v>
+        <v>-0.03651143143324219</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1166750287497185</v>
+        <v>-0.01350257553505048</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,19 +8588,19 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1320160740664619</v>
+        <v>0.01051378924740275</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0494238305793774</v>
+        <v>0.05816767464407226</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1865600003102084</v>
+        <v>0.05340879659909906</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
         <v>0</v>
@@ -8609,52 +8609,52 @@
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1730424271580917</v>
+        <v>0.1249776592992886</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.009388817905010597</v>
+        <v>-0.09980513170264614</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.06506810964786645</v>
+        <v>-0.03373623824935361</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.09986900044719299</v>
+        <v>-0.06408177268182139</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.002482990424373051</v>
+        <v>0.09530025727485704</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.01683375660035614</v>
+        <v>0.01756550923644718</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
         <v>0</v>
@@ -8663,31 +8663,31 @@
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.008155239770946721</v>
+        <v>-0.02838934245915373</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.08968021236295698</v>
+        <v>0.132400763984521</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.08419307435548569</v>
+        <v>0.02131564539069269</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>-0</v>
@@ -8696,46 +8696,46 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.06823981069395976</v>
+        <v>-0.06215565734773135</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.03993502049536606</v>
+        <v>0.1020982894836726</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.02198513537345884</v>
+        <v>0.02607475733305275</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.05340700110964001</v>
+        <v>-0.04167388733309448</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.05281677253042214</v>
+        <v>0.01649790729202812</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.03135123533190657</v>
+        <v>-0.03357477164684079</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
         <v>-0</v>
@@ -8750,25 +8750,25 @@
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.07612098666688269</v>
+        <v>-0.04994202883083703</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.00105686975117126</v>
+        <v>-0.02656367699302044</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.04071105581337536</v>
+        <v>-0.001994478297584867</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
@@ -8777,19 +8777,19 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.1061112957918297</v>
+        <v>0.01021802673092272</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.01344088079314381</v>
+        <v>0.06467872328333346</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.0360784858903925</v>
+        <v>-0.0390753512038817</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
@@ -8798,85 +8798,85 @@
         <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.08584084015662928</v>
+        <v>-0.03675083805764665</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.01374025550988224</v>
+        <v>0.07260466940171738</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.06326607711507953</v>
+        <v>0.05775029758416569</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.005464096826271214</v>
+        <v>0.005205315833124293</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0.007738225348544348</v>
+        <v>0.06485233666787814</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.02838655439194571</v>
+        <v>-0.02169196509746773</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.06845389075815903</v>
+        <v>-0.0634942871972948</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.0002996620343182189</v>
+        <v>0.1215263474154099</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01036299477839693</v>
+        <v>0.000614174661794195</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
@@ -8885,16 +8885,16 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.07638306644009481</v>
+        <v>0.1015969658770235</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.002004780392793349</v>
+        <v>0.07567486605322496</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.05023761619544669</v>
+        <v>-0.01249103791789524</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8903,31 +8903,31 @@
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.05371917675402176</v>
+        <v>0.02216835783731446</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.004241138105519327</v>
+        <v>0.1057484658235064</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.07338738210931368</v>
+        <v>-0.04012995523238511</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
         <v>-0</v>
@@ -8936,25 +8936,25 @@
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0683984955999119</v>
+        <v>-0.01201122371673352</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.1294700886360609</v>
+        <v>0.03559225152486455</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>0</v>
@@ -8965,10 +8965,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.383355218201992</v>
+        <v>0.5217358631936347</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08688097515846062</v>
+        <v>0.0193474555802788</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2713057766901324</v>
+        <v>-0.4469559588416702</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
@@ -8989,13 +8989,13 @@
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3203707006374342</v>
+        <v>0.6284927174080737</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,25 +9004,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.02068921724383613</v>
+        <v>-0.1609944677620418</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2161098511567084</v>
+        <v>-0.4588929942698236</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.04067789109711521</v>
+        <v>0.1429363037546409</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9031,40 +9031,40 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.06343202095551176</v>
+        <v>-0.1179751442302333</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.001192114902627322</v>
+        <v>-0.102827067984555</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.009435699379717095</v>
+        <v>-0.05010366380227511</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.007151742186560813</v>
+        <v>-0.2538859119471771</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.02187194387409443</v>
+        <v>0.1520224372484594</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,22 +9076,22 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.06127031395131687</v>
+        <v>0.124253010149618</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.009479966158627102</v>
+        <v>-0.05004699670778108</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.07423655049394527</v>
+        <v>-0.1002537223341192</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,37 +9100,37 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2572237188415533</v>
+        <v>0.7278557775461119</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.05943433957918837</v>
+        <v>-0.3366633998328752</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.1483747958467522</v>
+        <v>-0.3263677370113895</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.09918059249376278</v>
+        <v>-0.09813428184443299</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,52 +9139,52 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.05701949723824872</v>
+        <v>0.0440643140773596</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.08960157268331896</v>
+        <v>-0.05649112065265761</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.08756288521163136</v>
+        <v>0.1539212827062742</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.02839745591061479</v>
+        <v>0.07953536928007254</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.03130162377833199</v>
+        <v>0.1002225899075771</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1286138777639149</v>
+        <v>0.3445161402256838</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,40 +9193,40 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.04202070649757186</v>
+        <v>-0.0412135266224764</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.0668367540888372</v>
+        <v>-0.232018795395017</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.06614036786404286</v>
+        <v>-0.1805712140293463</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.004923396243971724</v>
+        <v>0.04780925289443345</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.06838183106333166</v>
+        <v>0.1345765122450788</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9238,46 +9238,46 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.008236099164519253</v>
+        <v>-0.2139117540994194</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.01236967884045602</v>
+        <v>0.1752390560546442</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.05034955857690645</v>
+        <v>0.01418546333557764</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.05746860441164812</v>
+        <v>-0.1694286588382403</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.00259200570868164</v>
+        <v>0.03742957118018634</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.07156612392391057</v>
+        <v>0.1754542128256036</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9286,25 +9286,25 @@
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.06721059119817049</v>
+        <v>-0.1629116077944654</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08476240123326297</v>
+        <v>-0.1303741492255025</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.001190528957544981</v>
+        <v>0.05698435899541892</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
@@ -9313,13 +9313,13 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.02422703330922944</v>
+        <v>-0.1079349471138915</v>
       </c>
       <c r="DP16" t="n">
         <v>0</v>
@@ -9328,16 +9328,16 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.02207722585386927</v>
+        <v>-0.01479685447397282</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0191594755821175</v>
+        <v>0.1660582948843559</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,76 +9346,76 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.05445364625276185</v>
+        <v>-0.03255323447546815</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.02856509248217596</v>
+        <v>0.04310961340575564</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.03747768440215937</v>
+        <v>0.03523306133982487</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.06107052198124852</v>
+        <v>-0.08191549119120635</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.01639663526925811</v>
+        <v>-0.005585295133644256</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.07160537168067808</v>
+        <v>0.0452857810680611</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO16" t="n">
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.04412268154229471</v>
+        <v>-0.09385661770925369</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.02934300354147326</v>
+        <v>-0.07382344766529711</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.02232011132291426</v>
+        <v>-0.005172429338190413</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9427,61 +9427,61 @@
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.05735767999770375</v>
+        <v>-0.2040704329997745</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.0008491699179714564</v>
+        <v>0.003420089348363218</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.07031905914136223</v>
+        <v>0.1436192075984493</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.0227141088496907</v>
+        <v>0.1423164467605891</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.001451930519993099</v>
+        <v>-0.05392893377147406</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.03763124305407049</v>
+        <v>0.1927777522498178</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.001192313746964836</v>
+        <v>0.0849278451084801</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,46 +9490,46 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.04524749916549141</v>
+        <v>-0.1092772114649071</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.03482332726166606</v>
+        <v>-0.1418879849774058</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.01903449972387808</v>
+        <v>-0.0002457240875876235</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.02736091518955155</v>
+        <v>0.2351642917688941</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2703503519746259</v>
+        <v>0.4025188119531994</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,16 +9546,16 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05164755262727126</v>
+        <v>-0.06319409014010842</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2462005779870592</v>
+        <v>-0.2064940126336064</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2355239707577025</v>
+        <v>0.4479619284617525</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,25 +9573,25 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0177343454435269</v>
+        <v>-0.2014108495525461</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1832742911866146</v>
+        <v>-0.2088524910255835</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.02024935006380167</v>
+        <v>0.1002640169625514</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -9600,37 +9600,37 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.02960735663090919</v>
+        <v>-0.1305177122673274</v>
       </c>
       <c r="X17" t="n">
-        <v>0.004843392224635812</v>
+        <v>-0.03512484666516319</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.01306537724971108</v>
+        <v>-0.04588373840951868</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.00981348346235867</v>
+        <v>-0.2369182773545992</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.01907193906736793</v>
+        <v>0.05113484076690058</v>
       </c>
       <c r="AH17" t="n">
         <v>-0</v>
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.04064149610339462</v>
+        <v>0.02749754487433688</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
@@ -9654,10 +9654,10 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.008325886038309836</v>
+        <v>-0.05447564597382713</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.03827930010684917</v>
+        <v>0.00941723720472982</v>
       </c>
       <c r="AQ17" t="n">
         <v>-0</v>
@@ -9669,10 +9669,10 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1903708024593827</v>
+        <v>0.4439540466516846</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,16 +9681,16 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.0375805256525377</v>
+        <v>-0.3021803832210047</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.1163770964105205</v>
+        <v>-0.1809799516591004</v>
       </c>
       <c r="AZ17" t="n">
         <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>0</v>
@@ -9699,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.06392834355267371</v>
+        <v>-0.01482575824842608</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,52 +9708,52 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.05743109644696862</v>
+        <v>-0.004712028552623098</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.09370277395270665</v>
+        <v>-0.06505221329473113</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.06695371915958219</v>
+        <v>0.06535124462658275</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01439711403269088</v>
+        <v>0.09313851021973113</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0214931088871881</v>
+        <v>0.007486198237156968</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.08843495512023875</v>
+        <v>0.2063544081561367</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,10 +9762,10 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.02275126168175346</v>
+        <v>-0.07958288308905885</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.03543297231431962</v>
+        <v>-0.08416039883667853</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9780,22 +9780,22 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.04110620763686845</v>
+        <v>-0.1094823155775881</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.007105235670135164</v>
+        <v>0.04080806965232163</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.05277784523685147</v>
+        <v>0.06907688403108576</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9804,52 +9804,52 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.004187188740740997</v>
+        <v>-0.1259214433592318</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.00563326547740629</v>
+        <v>0.1797706912124831</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.03200894429518685</v>
+        <v>0.1296366504973876</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.03079738580665582</v>
+        <v>-0.1106565936678291</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.004774148631888634</v>
+        <v>0.03554297657792787</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.05383557292468476</v>
+        <v>0.08888030773183192</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9858,49 +9858,49 @@
         <v>-0</v>
       </c>
       <c r="DE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.02736472341027946</v>
+        <v>-0.04519825622430419</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.03450336808904482</v>
+        <v>-0.1814058912960743</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.00620220376680639</v>
+        <v>0.03106110506057885</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.003134562540111374</v>
+        <v>0.01005826735917312</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01753413694738338</v>
+        <v>-0.09653295744609677</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.008737460757092001</v>
+        <v>0.07478890839711227</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
@@ -9909,13 +9909,13 @@
         <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.03379004973143529</v>
+        <v>0.004311217791080304</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
@@ -9924,10 +9924,10 @@
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.01120182053153756</v>
+        <v>-0.03323983823968547</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.02074746246215661</v>
+        <v>0.04089609165470441</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
@@ -9939,25 +9939,25 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.04598501371259419</v>
+        <v>-0.0602965001369289</v>
       </c>
       <c r="EH17" t="n">
         <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.004631449161900964</v>
+        <v>0.03547968502725508</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.06087764421370215</v>
+        <v>0.006605100612734243</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
@@ -9966,64 +9966,64 @@
         <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.0120828322566454</v>
+        <v>-0.02518727999404333</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.006466521312150383</v>
+        <v>0.007051259842113625</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.04174623419807377</v>
+        <v>0.1297718396250824</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.03042281153375468</v>
+        <v>-0.1251571863248816</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.0007437343737128045</v>
+        <v>0.01173492863141088</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.05402942243691884</v>
+        <v>0.05623466043306451</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.008900570996610733</v>
+        <v>0.2096641671259322</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
@@ -10032,16 +10032,16 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.000727802159421736</v>
+        <v>-0.1105925972559926</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01833434184775221</v>
+        <v>0.1414441945893039</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,46 +10050,46 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.01192454478545653</v>
+        <v>0.09083429951523768</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.0264905173746898</v>
+        <v>-0.1407428931483682</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0205018548043606</v>
+        <v>-0.06307811659968346</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.02238708401586274</v>
+        <v>-0.04063743774522161</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.03148434886869605</v>
+        <v>0.08857285027707552</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
@@ -10098,51 +10098,51 @@
         <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.544664586926812</v>
+        <v>-0.4231945472306166</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4507269175988999</v>
+        <v>0.4628869323746556</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1253814561918788</v>
+        <v>0.177153537019902</v>
       </c>
       <c r="F18" t="n">
         <v>-0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3649619387556648</v>
+        <v>-0.3971201744563061</v>
       </c>
       <c r="L18" t="n">
         <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4453305144303415</v>
+        <v>0.6115320828431655</v>
       </c>
       <c r="N18" t="n">
-        <v>0.08386426950315354</v>
+        <v>0.2372107260263545</v>
       </c>
       <c r="O18" t="n">
         <v>-0</v>
@@ -10151,88 +10151,88 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1432382416531448</v>
+        <v>0.02049992889975127</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0849386426760817</v>
+        <v>0.05661643421038469</v>
       </c>
       <c r="W18" t="n">
-        <v>0.04342108769856721</v>
+        <v>0.05227095978448053</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>-0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.1079891382871268</v>
+        <v>-0.03675139334880564</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.02010737718500687</v>
+        <v>0.02906199410828635</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.05469052021006245</v>
+        <v>-0.01856930464576418</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
         <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.07883420696287081</v>
+        <v>-0.1503478345879677</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.08136382411159085</v>
+        <v>0.03524462903935743</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.1225444535499565</v>
+        <v>-0.05658958486618728</v>
       </c>
       <c r="AP18" t="n">
         <v>-0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
         <v>-0</v>
@@ -10241,43 +10241,43 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>-0.4440235257928605</v>
+        <v>-0.3511644926789375</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.2088527531047631</v>
+        <v>0.1269460625343285</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.1041350049940881</v>
+        <v>0.2779565055237031</v>
       </c>
       <c r="AY18" t="n">
         <v>-0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
         <v>-0</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>-0.08008554567856918</v>
+        <v>0.01518708841656346</v>
       </c>
       <c r="BE18" t="n">
         <v>-0</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.06665382483967437</v>
+        <v>0.1160719335133261</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.1910129410679036</v>
+        <v>0.03424781999112256</v>
       </c>
       <c r="BH18" t="n">
         <v>-0</v>
@@ -10286,7 +10286,7 @@
         <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK18" t="n">
         <v>-0</v>
@@ -10295,22 +10295,22 @@
         <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>-0.0992762467709315</v>
+        <v>-0.03231155201635343</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>-0.06423718012852701</v>
+        <v>-0.1222033742404088</v>
       </c>
       <c r="BP18" t="n">
-        <v>-0.1432649462978008</v>
+        <v>-0.01276834103567715</v>
       </c>
       <c r="BQ18" t="n">
         <v>0</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS18" t="n">
         <v>0</v>
@@ -10322,16 +10322,16 @@
         <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>-0.1221481182699459</v>
+        <v>-0.1438767613371412</v>
       </c>
       <c r="BW18" t="n">
         <v>-0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.10741887936166</v>
+        <v>0.161804896175023</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.02717815601037591</v>
+        <v>0.04678597117084819</v>
       </c>
       <c r="BZ18" t="n">
         <v>-0</v>
@@ -10340,25 +10340,25 @@
         <v>0</v>
       </c>
       <c r="CB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.08740249252771197</v>
+        <v>0.1537945807219121</v>
       </c>
       <c r="CF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG18" t="n">
-        <v>-0.05760171445032051</v>
+        <v>-0.1224951776105677</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.01812953459794592</v>
+        <v>-0.02748485710336584</v>
       </c>
       <c r="CI18" t="n">
         <v>0</v>
@@ -10376,43 +10376,43 @@
         <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.04377532581875099</v>
+        <v>0.05711435652502116</v>
       </c>
       <c r="CO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.1014749095802093</v>
+        <v>-0.09267341328094873</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.03271101534861164</v>
+        <v>-0.1128211474376027</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS18" t="n">
         <v>0</v>
       </c>
       <c r="CT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.09238458682389075</v>
+        <v>0.1441039977662235</v>
       </c>
       <c r="CX18" t="n">
         <v>-0</v>
       </c>
       <c r="CY18" t="n">
-        <v>-0.08533563516868084</v>
+        <v>-0.1368504247647055</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.00794656534011701</v>
+        <v>-0.06271197618624422</v>
       </c>
       <c r="DA18" t="n">
         <v>-0</v>
@@ -10424,25 +10424,25 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE18" t="n">
         <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.03412776257557293</v>
+        <v>0.03489485738157855</v>
       </c>
       <c r="DG18" t="n">
         <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0.004957457644485312</v>
+        <v>0.02030223026884611</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.04968362250267638</v>
+        <v>0.009238468415778401</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10454,22 +10454,22 @@
         <v>-0</v>
       </c>
       <c r="DN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.01354323153063159</v>
+        <v>0.08923425923242849</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0.08695197519423302</v>
+        <v>-0.03753415192352696</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.04242991188487154</v>
+        <v>-0.0152739749000653</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT18" t="n">
         <v>0</v>
@@ -10481,28 +10481,28 @@
         <v>-0</v>
       </c>
       <c r="DW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.09162037765066608</v>
+        <v>0.09005319584387343</v>
       </c>
       <c r="DY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0.01086048985677346</v>
+        <v>-0.00831534942737496</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.01082215225111059</v>
+        <v>-0.02478895899049204</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE18" t="n">
         <v>0</v>
@@ -10511,49 +10511,49 @@
         <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.04559213656266076</v>
+        <v>0.1156939619696179</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>-0.09857226108128768</v>
+        <v>-0.07478901455082526</v>
       </c>
       <c r="EJ18" t="n">
-        <v>-0.04765914249669283</v>
+        <v>-0.05920701537202355</v>
       </c>
       <c r="EK18" t="n">
         <v>0</v>
       </c>
       <c r="EL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.1078157146825421</v>
+        <v>0.0625568831752894</v>
       </c>
       <c r="EQ18" t="n">
         <v>0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.04936934682760021</v>
+        <v>0.1175725240475981</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.04551021281071303</v>
+        <v>0.02511558638523313</v>
       </c>
       <c r="ET18" t="n">
         <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV18" t="n">
         <v>-0</v>
@@ -10562,19 +10562,19 @@
         <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.08646437552634491</v>
+        <v>0.1657707569218743</v>
       </c>
       <c r="EZ18" t="n">
         <v>0</v>
       </c>
       <c r="FA18" t="n">
-        <v>-0.07066004729972025</v>
+        <v>-0.1506446564282546</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.005007091491969836</v>
+        <v>-0.02984957162375156</v>
       </c>
       <c r="FC18" t="n">
         <v>0</v>
@@ -10583,58 +10583,58 @@
         <v>0</v>
       </c>
       <c r="FE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF18" t="n">
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>0.03544241326950621</v>
+        <v>-0.04243170150253082</v>
       </c>
       <c r="FI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>-0.09523958818787927</v>
+        <v>-0.1545344957184721</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.02492685009179059</v>
+        <v>0.01263786642727496</v>
       </c>
       <c r="FL18" t="n">
         <v>0</v>
       </c>
       <c r="FM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.01809268383377748</v>
+        <v>-0.05762396465002479</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
       </c>
       <c r="FS18" t="n">
-        <v>-0.08515641713649116</v>
+        <v>-0.03118977747735422</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.01356904424895642</v>
+        <v>0.07034601996892079</v>
       </c>
       <c r="FU18" t="n">
         <v>0</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
         <v>-0</v>
@@ -10643,31 +10643,31 @@
         <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.03588782440880015</v>
+        <v>0.06653527291711686</v>
       </c>
       <c r="GA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB18" t="n">
-        <v>0.08490766536909736</v>
+        <v>-0.05100575474885769</v>
       </c>
       <c r="GC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE18" t="n">
         <v>0</v>
       </c>
       <c r="GF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
